--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133829480</v>
       </c>
       <c r="B2" t="n">
-        <v>110093</v>
+        <v>110095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133829483</v>
       </c>
       <c r="B3" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133829486</v>
       </c>
       <c r="B4" t="n">
-        <v>97745</v>
+        <v>97747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133829480</v>
       </c>
       <c r="B2" t="n">
-        <v>110095</v>
+        <v>110101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133829483</v>
       </c>
       <c r="B3" t="n">
-        <v>97997</v>
+        <v>98003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133829486</v>
       </c>
       <c r="B4" t="n">
-        <v>97747</v>
+        <v>97753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133829480</v>
       </c>
       <c r="B2" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133829483</v>
       </c>
       <c r="B3" t="n">
-        <v>98003</v>
+        <v>98005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133829486</v>
       </c>
       <c r="B4" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133829480</v>
       </c>
       <c r="B2" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133829483</v>
       </c>
       <c r="B3" t="n">
-        <v>98005</v>
+        <v>98033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133829486</v>
       </c>
       <c r="B4" t="n">
-        <v>97755</v>
+        <v>97783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133829480</v>
       </c>
       <c r="B2" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133829483</v>
       </c>
       <c r="B3" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133829486</v>
       </c>
       <c r="B4" t="n">
-        <v>97783</v>
+        <v>97793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133829480</v>
       </c>
       <c r="B2" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133829480</v>
       </c>
       <c r="B2" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133829483</v>
       </c>
       <c r="B3" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133829486</v>
       </c>
       <c r="B4" t="n">
-        <v>97793</v>
+        <v>97795</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133829480</v>
       </c>
       <c r="B2" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133829483</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>133829486</v>
       </c>
       <c r="B4" t="n">
-        <v>97796</v>
+        <v>97803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133829480</v>
+        <v>133829485</v>
       </c>
       <c r="B2" t="n">
-        <v>110152</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411704</v>
+        <v>411870</v>
       </c>
       <c r="R2" t="n">
-        <v>6349850</v>
+        <v>6349912</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>granhögstubbe</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133829483</v>
+        <v>133829486</v>
       </c>
       <c r="B3" t="n">
-        <v>98053</v>
+        <v>97810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411855</v>
+        <v>411850</v>
       </c>
       <c r="R3" t="n">
-        <v>6349920</v>
+        <v>6349898</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133829486</v>
+        <v>133829480</v>
       </c>
       <c r="B4" t="n">
-        <v>97803</v>
+        <v>110159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411850</v>
+        <v>411704</v>
       </c>
       <c r="R4" t="n">
-        <v>6349898</v>
+        <v>6349850</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -963,6 +968,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133829483</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SV Högalid, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411855</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6349920</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Båraryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14432-2026 artfynd.xlsx
+++ b/artfynd/A 14432-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133829485</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133829486</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133829480</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,8 +1085,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133829483</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>